--- a/backend/wp_templates/H/H8 使用权资产.xlsx
+++ b/backend/wp_templates/H/H8 使用权资产.xlsx
@@ -28,11 +28,6 @@
     <sheet name="简化处理的租赁检查表H8-13" sheetId="21" r:id="rId19"/>
     <sheet name="关联交易检查表H8-14" sheetId="20" r:id="rId20"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId21"/>
-    <externalReference r:id="rId22"/>
-    <externalReference r:id="rId23"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'使用权资产 租赁负债初始及后续计量（按月）H8-6'!$A$21:$K$350</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">使用权资产实质性程序表H8A!$15:$16</definedName>
@@ -11413,410 +11408,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="底稿目录"/>
-      <sheetName val="使用权资产实质性程序表H8A"/>
-      <sheetName val="审定表H8-1"/>
-      <sheetName val="附注披露信息（上市公司）"/>
-      <sheetName val="附注披露信息（国企）"/>
-      <sheetName val="明细表H8-2"/>
-      <sheetName val="调整分录汇总H8-3"/>
-      <sheetName val="租赁的识别H8-4"/>
-      <sheetName val="租赁期的确定H8-5"/>
-      <sheetName val="使用权资产 租赁负责初始及后续计量（按年）H8-6"/>
-      <sheetName val="使用权资产 租赁负责初始及后续计量（按月）H8-6"/>
-      <sheetName val="租赁变更H8-7"/>
-      <sheetName val="折旧测算表（不含减值）H8-8"/>
-      <sheetName val="折旧测算表（含减值）H8-8"/>
-      <sheetName val="折旧分配分析表H8-9"/>
-      <sheetName val="减值测算表H8-10"/>
-      <sheetName val="可收回金额测试表H8-11"/>
-      <sheetName val="减少检查表H8-12"/>
-      <sheetName val="关联交易检查表H8-14"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>被审计单位：</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>截止日：202X年12月31日</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>编制人：</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>复核人：</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>编制日期：</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>复核日期：</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="底稿目录"/>
-      <sheetName val="使用权资产实质性程序表H8A"/>
-      <sheetName val="审定表H8-1"/>
-      <sheetName val="附注披露信息（上市公司）"/>
-      <sheetName val="附注披露信息（国企）"/>
-      <sheetName val="明细表H8-2"/>
-      <sheetName val="调整分录汇总H8-3"/>
-      <sheetName val="租赁的识别H8-4"/>
-      <sheetName val="租赁期的确定H8-5"/>
-      <sheetName val="使用权资产 租赁负责初始及后续计量（按年）H8-6"/>
-      <sheetName val="使用权资产 租赁负责初始及后续计量（按月）H8-6"/>
-      <sheetName val="租赁变更H8-7"/>
-      <sheetName val="折旧测算表（不含减值）H8-8"/>
-      <sheetName val="折旧测算表（含减值）H8-8"/>
-      <sheetName val="折旧分配分析表H8-9"/>
-      <sheetName val="可收回金额测试表H8-11"/>
-      <sheetName val="减少检查表H8-12"/>
-      <sheetName val="简化处理的租赁检查表H8-13"/>
-      <sheetName val="关联交易检查表H8-14"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>被审计单位：</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>截止日：202X年12月31日</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>编制人：</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>复核人：</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>编制日期：</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>复核日期：</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="底稿目录"/>
-      <sheetName val="使用权资产实质性程序表H8A"/>
-      <sheetName val="审定表H8-1"/>
-      <sheetName val="附注披露信息（上市公司）"/>
-      <sheetName val="附注披露信息（国企）"/>
-      <sheetName val="明细表H8-2"/>
-      <sheetName val="调整分录汇总H8-3"/>
-      <sheetName val="租赁的识别H8-4"/>
-      <sheetName val="租赁期的确定H8-5"/>
-      <sheetName val="使用权资产 租赁负责初始及后续计量（按年）H8-6"/>
-      <sheetName val="使用权资产 租赁负责初始及后续计量（按月）H8-6"/>
-      <sheetName val="租赁变更H8-7"/>
-      <sheetName val="折旧分配分析表H8-9"/>
-      <sheetName val="减值测算表H8-10"/>
-      <sheetName val="可收回金额测试表H8-11"/>
-      <sheetName val="减少检查表H8-12"/>
-      <sheetName val="简化处理的租赁检查表H8-13"/>
-      <sheetName val="关联交易检查表H8-14"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>被审计单位：</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>截止日：202X年12月31日</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>编制人：</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>复核人：</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>编制日期：</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>复核日期：</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
-        <row r="12">
-          <cell r="S12">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="AJ12">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="BA12">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="S13">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="AJ13">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="BA13">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="S14">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="AJ14">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="BA14">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="S15">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="AJ15">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="BA15">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="S16">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="AJ16">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="BA16">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="S28">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="AJ28">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="BA28">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="S29">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="AJ29">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="BA29">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="S30">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="AJ30">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="BA30">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="S31">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="AJ31">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="BA31">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33" t="str">
-            <v>其中：</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34" t="str">
-            <v>房屋及建筑物</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35" t="str">
-            <v>机器设备</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>运输设备</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>办公设备</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>其他设备</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
@@ -32992,17 +32583,17 @@
     </row>
     <row r="3" customHeight="1" spans="1:25">
       <c r="A3" s="269" t="str">
-        <f>[3]底稿目录!A2</f>
+        <f>底稿目录!A2</f>
         <v>被审计单位：</v>
       </c>
       <c r="B3" s="311"/>
       <c r="D3" s="270"/>
       <c r="E3" s="269" t="str">
-        <f>[3]底稿目录!A4</f>
+        <f>底稿目录!A4</f>
         <v>编制人：</v>
       </c>
       <c r="L3" s="269" t="str">
-        <f>[3]底稿目录!A6</f>
+        <f>底稿目录!A6</f>
         <v>编制日期：</v>
       </c>
       <c r="Q3" s="40" t="s">
@@ -33014,17 +32605,17 @@
     </row>
     <row r="4" customHeight="1" spans="1:25">
       <c r="A4" s="269" t="str">
-        <f>[3]底稿目录!A3</f>
+        <f>底稿目录!A3</f>
         <v>截止日：202X年12月31日</v>
       </c>
       <c r="B4" s="311"/>
       <c r="D4" s="270"/>
       <c r="E4" s="269" t="str">
-        <f>[3]底稿目录!A5</f>
+        <f>底稿目录!A5</f>
         <v>复核人：</v>
       </c>
       <c r="L4" s="269" t="str">
-        <f>[3]底稿目录!A7</f>
+        <f>底稿目录!A7</f>
         <v>复核日期：</v>
       </c>
       <c r="Q4" s="40" t="s">
@@ -33144,23 +32735,23 @@
     </row>
     <row r="9" s="264" customFormat="1" customHeight="1" spans="1:25">
       <c r="A9" s="320">
-        <f>'[3]明细表H8-2'!A12</f>
+        <f>'明细表H8-2'!A12</f>
         <v>0</v>
       </c>
       <c r="B9" s="320">
-        <f>'[3]明细表H8-2'!B12</f>
+        <f>'明细表H8-2'!B12</f>
         <v>0</v>
       </c>
       <c r="C9" s="320">
-        <f>'[3]明细表H8-2'!C12</f>
+        <f>'明细表H8-2'!C12</f>
         <v>0</v>
       </c>
       <c r="D9" s="321">
-        <f>'[3]明细表H8-2'!S12</f>
+        <f>'明细表H8-2'!S12</f>
         <v>0</v>
       </c>
       <c r="E9" s="321">
-        <f>'[3]明细表H8-2'!AJ12</f>
+        <f>'明细表H8-2'!AJ12</f>
         <v>0</v>
       </c>
       <c r="F9" s="283"/>
@@ -33206,23 +32797,23 @@
     </row>
     <row r="10" s="264" customFormat="1" customHeight="1" spans="1:25">
       <c r="A10" s="320">
-        <f>'[3]明细表H8-2'!A13</f>
+        <f>'明细表H8-2'!A13</f>
         <v>0</v>
       </c>
       <c r="B10" s="320">
-        <f>'[3]明细表H8-2'!B13</f>
+        <f>'明细表H8-2'!B13</f>
         <v>0</v>
       </c>
       <c r="C10" s="320">
-        <f>'[3]明细表H8-2'!C13</f>
+        <f>'明细表H8-2'!C13</f>
         <v>0</v>
       </c>
       <c r="D10" s="321">
-        <f>'[3]明细表H8-2'!S13</f>
+        <f>'明细表H8-2'!S13</f>
         <v>0</v>
       </c>
       <c r="E10" s="321">
-        <f>'[3]明细表H8-2'!AJ13</f>
+        <f>'明细表H8-2'!AJ13</f>
         <v>0</v>
       </c>
       <c r="F10" s="283"/>
@@ -33268,23 +32859,23 @@
     </row>
     <row r="11" customHeight="1" spans="1:25">
       <c r="A11" s="320">
-        <f>'[3]明细表H8-2'!A14</f>
+        <f>'明细表H8-2'!A14</f>
         <v>0</v>
       </c>
       <c r="B11" s="320">
-        <f>'[3]明细表H8-2'!B14</f>
+        <f>'明细表H8-2'!B14</f>
         <v>0</v>
       </c>
       <c r="C11" s="320">
-        <f>'[3]明细表H8-2'!C14</f>
+        <f>'明细表H8-2'!C14</f>
         <v>0</v>
       </c>
       <c r="D11" s="321">
-        <f>'[3]明细表H8-2'!S14</f>
+        <f>'明细表H8-2'!S14</f>
         <v>0</v>
       </c>
       <c r="E11" s="321">
-        <f>'[3]明细表H8-2'!AJ14</f>
+        <f>'明细表H8-2'!AJ14</f>
         <v>0</v>
       </c>
       <c r="F11" s="283"/>
@@ -33330,23 +32921,23 @@
     </row>
     <row r="12" customHeight="1" spans="1:25">
       <c r="A12" s="320">
-        <f>'[3]明细表H8-2'!A15</f>
+        <f>'明细表H8-2'!A15</f>
         <v>0</v>
       </c>
       <c r="B12" s="320">
-        <f>'[3]明细表H8-2'!B15</f>
+        <f>'明细表H8-2'!B15</f>
         <v>0</v>
       </c>
       <c r="C12" s="320">
-        <f>'[3]明细表H8-2'!C15</f>
+        <f>'明细表H8-2'!C15</f>
         <v>0</v>
       </c>
       <c r="D12" s="321">
-        <f>'[3]明细表H8-2'!S15</f>
+        <f>'明细表H8-2'!S15</f>
         <v>0</v>
       </c>
       <c r="E12" s="321">
-        <f>'[3]明细表H8-2'!AJ15</f>
+        <f>'明细表H8-2'!AJ15</f>
         <v>0</v>
       </c>
       <c r="F12" s="283"/>
@@ -33392,23 +32983,23 @@
     </row>
     <row r="13" customHeight="1" spans="1:25">
       <c r="A13" s="320">
-        <f>'[3]明细表H8-2'!A16</f>
+        <f>'明细表H8-2'!A16</f>
         <v>0</v>
       </c>
       <c r="B13" s="320">
-        <f>'[3]明细表H8-2'!B16</f>
+        <f>'明细表H8-2'!B16</f>
         <v>0</v>
       </c>
       <c r="C13" s="320">
-        <f>'[3]明细表H8-2'!C16</f>
+        <f>'明细表H8-2'!C16</f>
         <v>0</v>
       </c>
       <c r="D13" s="321">
-        <f>'[3]明细表H8-2'!S16</f>
+        <f>'明细表H8-2'!S16</f>
         <v>0</v>
       </c>
       <c r="E13" s="321">
-        <f>'[3]明细表H8-2'!AJ16</f>
+        <f>'明细表H8-2'!AJ16</f>
         <v>0</v>
       </c>
       <c r="F13" s="283"/>
@@ -33497,7 +33088,7 @@
     </row>
     <row r="15" s="306" customFormat="1" customHeight="1" spans="1:25">
       <c r="A15" s="327" t="str">
-        <f>'[3]明细表H8-2'!A33:C33</f>
+        <f>'明细表H8-2'!A33:C33</f>
         <v>其中：</v>
       </c>
       <c r="B15" s="119"/>
@@ -33520,7 +33111,7 @@
     </row>
     <row r="16" s="306" customFormat="1" customHeight="1" spans="1:25">
       <c r="A16" s="327" t="str">
-        <f>'[3]明细表H8-2'!A34:C34</f>
+        <f>'明细表H8-2'!A34:C34</f>
         <v>房屋及建筑物</v>
       </c>
       <c r="B16" s="119"/>
@@ -33564,7 +33155,7 @@
     </row>
     <row r="17" s="306" customFormat="1" customHeight="1" spans="1:18">
       <c r="A17" s="327" t="str">
-        <f>'[3]明细表H8-2'!A35:C35</f>
+        <f>'明细表H8-2'!A35:C35</f>
         <v>机器设备</v>
       </c>
       <c r="B17" s="119"/>
@@ -33608,7 +33199,7 @@
     </row>
     <row r="18" s="306" customFormat="1" customHeight="1" spans="1:18">
       <c r="A18" s="327" t="str">
-        <f>'[3]明细表H8-2'!A36:C36</f>
+        <f>'明细表H8-2'!A36:C36</f>
         <v>运输设备</v>
       </c>
       <c r="B18" s="119"/>
@@ -33652,7 +33243,7 @@
     </row>
     <row r="19" s="306" customFormat="1" customHeight="1" spans="1:18">
       <c r="A19" s="327" t="str">
-        <f>'[3]明细表H8-2'!A37:C37</f>
+        <f>'明细表H8-2'!A37:C37</f>
         <v>办公设备</v>
       </c>
       <c r="B19" s="119"/>
@@ -33696,7 +33287,7 @@
     </row>
     <row r="20" s="306" customFormat="1" customHeight="1" spans="1:18">
       <c r="A20" s="327" t="str">
-        <f>'[3]明细表H8-2'!A38:C38</f>
+        <f>'明细表H8-2'!A38:C38</f>
         <v>其他设备</v>
       </c>
       <c r="B20" s="119"/>
@@ -33906,17 +33497,17 @@
     </row>
     <row r="3" customHeight="1" spans="1:27">
       <c r="A3" s="34" t="str">
-        <f>[3]底稿目录!A2</f>
+        <f>底稿目录!A2</f>
         <v>被审计单位：</v>
       </c>
       <c r="B3" s="36"/>
       <c r="D3" s="214"/>
       <c r="E3" s="34" t="str">
-        <f>[3]底稿目录!A4</f>
+        <f>底稿目录!A4</f>
         <v>编制人：</v>
       </c>
       <c r="Q3" s="34" t="str">
-        <f>[3]底稿目录!A6</f>
+        <f>底稿目录!A6</f>
         <v>编制日期：</v>
       </c>
       <c r="R3" s="39"/>
@@ -33929,17 +33520,17 @@
     </row>
     <row r="4" customHeight="1" spans="1:27">
       <c r="A4" s="34" t="str">
-        <f>[3]底稿目录!A3</f>
+        <f>底稿目录!A3</f>
         <v>截止日：202X年12月31日</v>
       </c>
       <c r="B4" s="36"/>
       <c r="D4" s="214"/>
       <c r="E4" s="34" t="str">
-        <f>[3]底稿目录!A5</f>
+        <f>底稿目录!A5</f>
         <v>复核人：</v>
       </c>
       <c r="Q4" s="34" t="str">
-        <f>[3]底稿目录!A7</f>
+        <f>底稿目录!A7</f>
         <v>复核日期：</v>
       </c>
       <c r="R4" s="39"/>
@@ -34092,27 +33683,27 @@
     </row>
     <row r="9" s="264" customFormat="1" customHeight="1" spans="1:27">
       <c r="A9" s="281">
-        <f>'[3]明细表H8-2'!A12</f>
+        <f>'明细表H8-2'!A12</f>
         <v>0</v>
       </c>
       <c r="B9" s="281">
-        <f>'[3]明细表H8-2'!B12</f>
+        <f>'明细表H8-2'!B12</f>
         <v>0</v>
       </c>
       <c r="C9" s="281">
-        <f>'[3]明细表H8-2'!C12</f>
+        <f>'明细表H8-2'!C12</f>
         <v>0</v>
       </c>
       <c r="D9" s="282">
-        <f>'[3]明细表H8-2'!S12</f>
+        <f>'明细表H8-2'!S12</f>
         <v>0</v>
       </c>
       <c r="E9" s="282">
-        <f>'[3]明细表H8-2'!AJ12</f>
+        <f>'明细表H8-2'!AJ12</f>
         <v>0</v>
       </c>
       <c r="F9" s="282">
-        <f>'[3]明细表H8-2'!BA12</f>
+        <f>'明细表H8-2'!BA12</f>
         <v>0</v>
       </c>
       <c r="G9" s="283"/>
@@ -34178,27 +33769,27 @@
     </row>
     <row r="10" s="264" customFormat="1" customHeight="1" spans="1:27">
       <c r="A10" s="281">
-        <f>'[3]明细表H8-2'!A13</f>
+        <f>'明细表H8-2'!A13</f>
         <v>0</v>
       </c>
       <c r="B10" s="281">
-        <f>'[3]明细表H8-2'!B13</f>
+        <f>'明细表H8-2'!B13</f>
         <v>0</v>
       </c>
       <c r="C10" s="281">
-        <f>'[3]明细表H8-2'!C13</f>
+        <f>'明细表H8-2'!C13</f>
         <v>0</v>
       </c>
       <c r="D10" s="282">
-        <f>'[3]明细表H8-2'!S13</f>
+        <f>'明细表H8-2'!S13</f>
         <v>0</v>
       </c>
       <c r="E10" s="282">
-        <f>'[3]明细表H8-2'!AJ13</f>
+        <f>'明细表H8-2'!AJ13</f>
         <v>0</v>
       </c>
       <c r="F10" s="282">
-        <f>'[3]明细表H8-2'!BA13</f>
+        <f>'明细表H8-2'!BA13</f>
         <v>0</v>
       </c>
       <c r="G10" s="283"/>
@@ -34264,27 +33855,27 @@
     </row>
     <row r="11" customHeight="1" spans="1:27">
       <c r="A11" s="281">
-        <f>'[3]明细表H8-2'!A14</f>
+        <f>'明细表H8-2'!A14</f>
         <v>0</v>
       </c>
       <c r="B11" s="281">
-        <f>'[3]明细表H8-2'!B14</f>
+        <f>'明细表H8-2'!B14</f>
         <v>0</v>
       </c>
       <c r="C11" s="281">
-        <f>'[3]明细表H8-2'!C14</f>
+        <f>'明细表H8-2'!C14</f>
         <v>0</v>
       </c>
       <c r="D11" s="282">
-        <f>'[3]明细表H8-2'!S14</f>
+        <f>'明细表H8-2'!S14</f>
         <v>0</v>
       </c>
       <c r="E11" s="282">
-        <f>'[3]明细表H8-2'!AJ14</f>
+        <f>'明细表H8-2'!AJ14</f>
         <v>0</v>
       </c>
       <c r="F11" s="282">
-        <f>'[3]明细表H8-2'!BA14</f>
+        <f>'明细表H8-2'!BA14</f>
         <v>0</v>
       </c>
       <c r="G11" s="283"/>
@@ -34350,27 +33941,27 @@
     </row>
     <row r="12" customHeight="1" spans="1:27">
       <c r="A12" s="281">
-        <f>'[3]明细表H8-2'!A15</f>
+        <f>'明细表H8-2'!A15</f>
         <v>0</v>
       </c>
       <c r="B12" s="281">
-        <f>'[3]明细表H8-2'!B15</f>
+        <f>'明细表H8-2'!B15</f>
         <v>0</v>
       </c>
       <c r="C12" s="281">
-        <f>'[3]明细表H8-2'!C15</f>
+        <f>'明细表H8-2'!C15</f>
         <v>0</v>
       </c>
       <c r="D12" s="282">
-        <f>'[3]明细表H8-2'!S15</f>
+        <f>'明细表H8-2'!S15</f>
         <v>0</v>
       </c>
       <c r="E12" s="282">
-        <f>'[3]明细表H8-2'!AJ15</f>
+        <f>'明细表H8-2'!AJ15</f>
         <v>0</v>
       </c>
       <c r="F12" s="282">
-        <f>'[3]明细表H8-2'!BA15</f>
+        <f>'明细表H8-2'!BA15</f>
         <v>0</v>
       </c>
       <c r="G12" s="283"/>
@@ -34436,27 +34027,27 @@
     </row>
     <row r="13" customHeight="1" spans="1:27">
       <c r="A13" s="281">
-        <f>'[3]明细表H8-2'!A16</f>
+        <f>'明细表H8-2'!A16</f>
         <v>0</v>
       </c>
       <c r="B13" s="281">
-        <f>'[3]明细表H8-2'!B16</f>
+        <f>'明细表H8-2'!B16</f>
         <v>0</v>
       </c>
       <c r="C13" s="281">
-        <f>'[3]明细表H8-2'!C16</f>
+        <f>'明细表H8-2'!C16</f>
         <v>0</v>
       </c>
       <c r="D13" s="282">
-        <f>'[3]明细表H8-2'!S16</f>
+        <f>'明细表H8-2'!S16</f>
         <v>0</v>
       </c>
       <c r="E13" s="282">
-        <f>'[3]明细表H8-2'!AJ16</f>
+        <f>'明细表H8-2'!AJ16</f>
         <v>0</v>
       </c>
       <c r="F13" s="282">
-        <f>'[3]明细表H8-2'!BA16</f>
+        <f>'明细表H8-2'!BA16</f>
         <v>0</v>
       </c>
       <c r="G13" s="283"/>
@@ -34522,27 +34113,27 @@
     </row>
     <row r="14" customHeight="1" spans="1:27">
       <c r="A14" s="281">
-        <f>'[3]明细表H8-2'!A28</f>
+        <f>'明细表H8-2'!A28</f>
         <v>0</v>
       </c>
       <c r="B14" s="281">
-        <f>'[3]明细表H8-2'!B28</f>
+        <f>'明细表H8-2'!B28</f>
         <v>0</v>
       </c>
       <c r="C14" s="281">
-        <f>'[3]明细表H8-2'!C28</f>
+        <f>'明细表H8-2'!C28</f>
         <v>0</v>
       </c>
       <c r="D14" s="282">
-        <f>'[3]明细表H8-2'!S28</f>
+        <f>'明细表H8-2'!S28</f>
         <v>0</v>
       </c>
       <c r="E14" s="282">
-        <f>'[3]明细表H8-2'!AJ28</f>
+        <f>'明细表H8-2'!AJ28</f>
         <v>0</v>
       </c>
       <c r="F14" s="282">
-        <f>'[3]明细表H8-2'!BA28</f>
+        <f>'明细表H8-2'!BA28</f>
         <v>0</v>
       </c>
       <c r="G14" s="283"/>
@@ -34608,27 +34199,27 @@
     </row>
     <row r="15" customHeight="1" spans="1:27">
       <c r="A15" s="281">
-        <f>'[3]明细表H8-2'!A29</f>
+        <f>'明细表H8-2'!A29</f>
         <v>0</v>
       </c>
       <c r="B15" s="281">
-        <f>'[3]明细表H8-2'!B29</f>
+        <f>'明细表H8-2'!B29</f>
         <v>0</v>
       </c>
       <c r="C15" s="281">
-        <f>'[3]明细表H8-2'!C29</f>
+        <f>'明细表H8-2'!C29</f>
         <v>0</v>
       </c>
       <c r="D15" s="282">
-        <f>'[3]明细表H8-2'!S29</f>
+        <f>'明细表H8-2'!S29</f>
         <v>0</v>
       </c>
       <c r="E15" s="282">
-        <f>'[3]明细表H8-2'!AJ29</f>
+        <f>'明细表H8-2'!AJ29</f>
         <v>0</v>
       </c>
       <c r="F15" s="282">
-        <f>'[3]明细表H8-2'!BA29</f>
+        <f>'明细表H8-2'!BA29</f>
         <v>0</v>
       </c>
       <c r="G15" s="283"/>
@@ -34694,27 +34285,27 @@
     </row>
     <row r="16" customHeight="1" spans="1:27">
       <c r="A16" s="281">
-        <f>'[3]明细表H8-2'!A30</f>
+        <f>'明细表H8-2'!A30</f>
         <v>0</v>
       </c>
       <c r="B16" s="281">
-        <f>'[3]明细表H8-2'!B30</f>
+        <f>'明细表H8-2'!B30</f>
         <v>0</v>
       </c>
       <c r="C16" s="281">
-        <f>'[3]明细表H8-2'!C30</f>
+        <f>'明细表H8-2'!C30</f>
         <v>0</v>
       </c>
       <c r="D16" s="282">
-        <f>'[3]明细表H8-2'!S30</f>
+        <f>'明细表H8-2'!S30</f>
         <v>0</v>
       </c>
       <c r="E16" s="282">
-        <f>'[3]明细表H8-2'!AJ30</f>
+        <f>'明细表H8-2'!AJ30</f>
         <v>0</v>
       </c>
       <c r="F16" s="282">
-        <f>'[3]明细表H8-2'!BA30</f>
+        <f>'明细表H8-2'!BA30</f>
         <v>0</v>
       </c>
       <c r="G16" s="283"/>
@@ -34780,27 +34371,27 @@
     </row>
     <row r="17" customHeight="1" spans="1:24">
       <c r="A17" s="281">
-        <f>'[3]明细表H8-2'!A31</f>
+        <f>'明细表H8-2'!A31</f>
         <v>0</v>
       </c>
       <c r="B17" s="281">
-        <f>'[3]明细表H8-2'!B31</f>
+        <f>'明细表H8-2'!B31</f>
         <v>0</v>
       </c>
       <c r="C17" s="281">
-        <f>'[3]明细表H8-2'!C31</f>
+        <f>'明细表H8-2'!C31</f>
         <v>0</v>
       </c>
       <c r="D17" s="282">
-        <f>'[3]明细表H8-2'!S31</f>
+        <f>'明细表H8-2'!S31</f>
         <v>0</v>
       </c>
       <c r="E17" s="282">
-        <f>'[3]明细表H8-2'!AJ31</f>
+        <f>'明细表H8-2'!AJ31</f>
         <v>0</v>
       </c>
       <c r="F17" s="282">
-        <f>'[3]明细表H8-2'!BA31</f>
+        <f>'明细表H8-2'!BA31</f>
         <v>0</v>
       </c>
       <c r="G17" s="283"/>
@@ -34921,7 +34512,7 @@
     </row>
     <row r="19" s="266" customFormat="1" customHeight="1" spans="1:24">
       <c r="A19" s="295" t="str">
-        <f>'[3]明细表H8-2'!A33:C33</f>
+        <f>'明细表H8-2'!A33:C33</f>
         <v>其中：</v>
       </c>
       <c r="B19" s="119"/>
@@ -34950,7 +34541,7 @@
     </row>
     <row r="20" s="266" customFormat="1" customHeight="1" spans="1:24">
       <c r="A20" s="295" t="str">
-        <f>'[3]明细表H8-2'!A34:C34</f>
+        <f>'明细表H8-2'!A34:C34</f>
         <v>房屋及建筑物</v>
       </c>
       <c r="B20" s="119"/>
@@ -35015,7 +34606,7 @@
     </row>
     <row r="21" s="266" customFormat="1" customHeight="1" spans="1:24">
       <c r="A21" s="295" t="str">
-        <f>'[3]明细表H8-2'!A35:C35</f>
+        <f>'明细表H8-2'!A35:C35</f>
         <v>机器设备</v>
       </c>
       <c r="B21" s="119"/>
@@ -35080,7 +34671,7 @@
     </row>
     <row r="22" s="266" customFormat="1" customHeight="1" spans="1:24">
       <c r="A22" s="295" t="str">
-        <f>'[3]明细表H8-2'!A36:C36</f>
+        <f>'明细表H8-2'!A36:C36</f>
         <v>运输设备</v>
       </c>
       <c r="B22" s="119"/>
@@ -35145,7 +34736,7 @@
     </row>
     <row r="23" s="266" customFormat="1" customHeight="1" spans="1:24">
       <c r="A23" s="295" t="str">
-        <f>'[3]明细表H8-2'!A37:C37</f>
+        <f>'明细表H8-2'!A37:C37</f>
         <v>办公设备</v>
       </c>
       <c r="B23" s="119"/>
@@ -35210,7 +34801,7 @@
     </row>
     <row r="24" s="266" customFormat="1" customHeight="1" spans="1:24">
       <c r="A24" s="295" t="str">
-        <f>'[3]明细表H8-2'!A38:C38</f>
+        <f>'明细表H8-2'!A38:C38</f>
         <v>其他设备</v>
       </c>
       <c r="B24" s="119"/>
@@ -35724,16 +35315,16 @@
     </row>
     <row r="3" customHeight="1" spans="1:32">
       <c r="A3" s="34" t="str">
-        <f>[2]底稿目录!A2</f>
+        <f>底稿目录!A2</f>
         <v>被审计单位：</v>
       </c>
       <c r="E3" s="34" t="str">
-        <f>[2]底稿目录!A4</f>
+        <f>底稿目录!A4</f>
         <v>编制人：</v>
       </c>
       <c r="G3" s="209"/>
       <c r="H3" s="34" t="str">
-        <f>[2]底稿目录!A6</f>
+        <f>底稿目录!A6</f>
         <v>编制日期：</v>
       </c>
       <c r="K3" s="40" t="s">
@@ -35745,16 +35336,16 @@
     </row>
     <row r="4" customHeight="1" spans="1:32">
       <c r="A4" s="34" t="str">
-        <f>[2]底稿目录!A3</f>
+        <f>底稿目录!A3</f>
         <v>截止日：202X年12月31日</v>
       </c>
       <c r="E4" s="34" t="str">
-        <f>[2]底稿目录!A5</f>
+        <f>底稿目录!A5</f>
         <v>复核人：</v>
       </c>
       <c r="G4" s="209"/>
       <c r="H4" s="34" t="str">
-        <f>[2]底稿目录!A7</f>
+        <f>底稿目录!A7</f>
         <v>复核日期：</v>
       </c>
       <c r="K4" s="40" t="s">
@@ -38453,15 +38044,15 @@
     </row>
     <row r="3" customHeight="1" spans="1:18">
       <c r="A3" s="34" t="str">
-        <f>[1]底稿目录!A2</f>
+        <f>底稿目录!A2</f>
         <v>被审计单位：</v>
       </c>
       <c r="E3" s="36" t="str">
-        <f>[1]底稿目录!A4</f>
+        <f>底稿目录!A4</f>
         <v>编制人：</v>
       </c>
       <c r="K3" s="34" t="str">
-        <f>[1]底稿目录!A6</f>
+        <f>底稿目录!A6</f>
         <v>编制日期：</v>
       </c>
       <c r="L3" s="39"/>
@@ -38474,15 +38065,15 @@
     </row>
     <row r="4" customHeight="1" spans="1:18">
       <c r="A4" s="34" t="str">
-        <f>[1]底稿目录!A3</f>
+        <f>底稿目录!A3</f>
         <v>截止日：202X年12月31日</v>
       </c>
       <c r="E4" s="36" t="str">
-        <f>[1]底稿目录!A5</f>
+        <f>底稿目录!A5</f>
         <v>复核人：</v>
       </c>
       <c r="K4" s="34" t="str">
-        <f>[1]底稿目录!A7</f>
+        <f>底稿目录!A7</f>
         <v>复核日期：</v>
       </c>
       <c r="L4" s="39"/>
